--- a/data/trans_orig/P6712-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6712-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que tenga iniciativa en 2012</t>
+          <t>Población según si su trabajo requiere que tenga iniciativa en 2012 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>15439</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11152</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28609</t>
+          <t>28379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20028</t>
+          <t>21646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13009</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>11238</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29274</t>
+          <t>29668</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19529</t>
+          <t>18974</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39772</t>
+          <t>38953</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12622</t>
+          <t>12847</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30212</t>
+          <t>30261</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36664</t>
+          <t>37115</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65091</t>
+          <t>64197</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29503</t>
+          <t>29779</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>52462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14771</t>
+          <t>14375</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32132</t>
+          <t>32469</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48913</t>
+          <t>48191</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77513</t>
+          <t>76795</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80391</t>
+          <t>80903</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107754</t>
+          <t>107180</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65092</t>
+          <t>65508</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89972</t>
+          <t>89614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>155181</t>
+          <t>153881</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190463</t>
+          <t>188704</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>58,79%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32873</t>
+          <t>32897</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60501</t>
+          <t>58529</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>17567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36393</t>
+          <t>36882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55133</t>
+          <t>55366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88086</t>
+          <t>89698</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30462</t>
+          <t>29580</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57450</t>
+          <t>56930</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41184</t>
+          <t>40593</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53526</t>
+          <t>54772</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87676</t>
+          <t>87860</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>142809</t>
+          <t>143074</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>188170</t>
+          <t>192432</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95702</t>
+          <t>94301</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>132683</t>
+          <t>133545</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>248563</t>
+          <t>252203</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>307906</t>
+          <t>310795</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>200793</t>
+          <t>200819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>253778</t>
+          <t>253029</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>148122</t>
+          <t>148900</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>192001</t>
+          <t>194451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>363699</t>
+          <t>363115</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>430640</t>
+          <t>429752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>403696</t>
+          <t>404304</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>469160</t>
+          <t>466069</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>208367</t>
+          <t>207146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>256471</t>
+          <t>255636</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>632271</t>
+          <t>627682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>708204</t>
+          <t>706862</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14548</t>
+          <t>13922</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>22155</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21776</t>
+          <t>23573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28897</t>
+          <t>27993</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>17148</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39186</t>
+          <t>40480</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>19353</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42953</t>
+          <t>41645</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>42367</t>
+          <t>42396</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75322</t>
+          <t>74171</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53867</t>
+          <t>53609</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83801</t>
+          <t>82879</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37262</t>
+          <t>36316</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63778</t>
+          <t>64517</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>98809</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>138271</t>
+          <t>139278</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182494</t>
+          <t>182348</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>218185</t>
+          <t>220513</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>126094</t>
+          <t>126880</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159124</t>
+          <t>158471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>319196</t>
+          <t>319994</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>367653</t>
+          <t>369507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,29%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45232</t>
+          <t>44708</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77192</t>
+          <t>75999</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31330</t>
+          <t>31491</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56261</t>
+          <t>57776</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84719</t>
+          <t>84730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>123500</t>
+          <t>125325</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>49646</t>
+          <t>50771</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>84363</t>
+          <t>83832</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29522</t>
+          <t>28084</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53604</t>
+          <t>53865</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>84682</t>
+          <t>86802</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>126098</t>
+          <t>129959</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>195114</t>
+          <t>193698</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>250328</t>
+          <t>251471</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>141745</t>
+          <t>142484</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>186230</t>
+          <t>190951</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>350323</t>
+          <t>349554</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>425991</t>
+          <t>421567</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>300212</t>
+          <t>303778</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>363550</t>
+          <t>367283</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>215825</t>
+          <t>214748</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>274056</t>
+          <t>272250</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>534550</t>
+          <t>534499</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>619683</t>
+          <t>621035</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>694195</t>
+          <t>692292</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>770843</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>416240</t>
+          <t>418672</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>482329</t>
+          <t>483613</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1132355</t>
+          <t>1130142</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1232650</t>
+          <t>1235238</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,51%</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que tenga iniciativa en 2016</t>
+          <t>Población según si su trabajo requiere que tenga iniciativa en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9997</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26318</t>
+          <t>25777</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15289</t>
+          <t>15149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>16273</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35269</t>
+          <t>35943</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25866</t>
+          <t>25747</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14745</t>
+          <t>13959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35401</t>
+          <t>35625</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22688</t>
+          <t>22599</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43100</t>
+          <t>43555</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>16652</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33166</t>
+          <t>32061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44534</t>
+          <t>43112</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70706</t>
+          <t>69767</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41483</t>
+          <t>41249</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20396</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33669</t>
+          <t>32958</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56749</t>
+          <t>57197</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35504</t>
+          <t>36059</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58259</t>
+          <t>59142</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26527</t>
+          <t>27896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51206</t>
+          <t>52120</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>79919</t>
+          <t>80011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30791</t>
+          <t>32307</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59334</t>
+          <t>60526</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28183</t>
+          <t>28016</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>53124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63735</t>
+          <t>65166</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103404</t>
+          <t>100562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67802</t>
+          <t>66849</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104232</t>
+          <t>101691</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54395</t>
+          <t>56537</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86835</t>
+          <t>86783</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131117</t>
+          <t>131796</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>180838</t>
+          <t>177707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>186507</t>
+          <t>186119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>240135</t>
+          <t>239597</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>133179</t>
+          <t>132761</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>176858</t>
+          <t>175122</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332360</t>
+          <t>332418</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>402506</t>
+          <t>401830</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>249222</t>
+          <t>250360</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>305591</t>
+          <t>307835</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>173988</t>
+          <t>176843</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>225021</t>
+          <t>224415</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>439844</t>
+          <t>444290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>513675</t>
+          <t>515806</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>277624</t>
+          <t>278688</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>337442</t>
+          <t>337281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>166370</t>
+          <t>167223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>215991</t>
+          <t>212615</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>462123</t>
+          <t>460440</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>540729</t>
+          <t>537041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15353</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21289</t>
+          <t>19719</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>11366</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28780</t>
+          <t>28956</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35363</t>
+          <t>34860</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15512</t>
+          <t>15218</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34223</t>
+          <t>32914</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34612</t>
+          <t>34883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61053</t>
+          <t>62452</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46202</t>
+          <t>46366</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78284</t>
+          <t>77290</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39858</t>
+          <t>38865</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66490</t>
+          <t>66345</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>94792</t>
+          <t>92772</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>136292</t>
+          <t>131818</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67247</t>
+          <t>68579</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>101252</t>
+          <t>102119</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50477</t>
+          <t>49874</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79064</t>
+          <t>79766</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>123977</t>
+          <t>127416</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169837</t>
+          <t>170745</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153387</t>
+          <t>154482</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193922</t>
+          <t>193238</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>141661</t>
+          <t>142031</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>177084</t>
+          <t>176765</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>307046</t>
+          <t>307179</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>358577</t>
+          <t>360032</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53246</t>
+          <t>52589</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87757</t>
+          <t>85275</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45340</t>
+          <t>44878</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74386</t>
+          <t>75302</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>104292</t>
+          <t>106272</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>148368</t>
+          <t>150786</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>104085</t>
+          <t>104960</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>147916</t>
+          <t>149957</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>84520</t>
+          <t>85276</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>123225</t>
+          <t>121771</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>196586</t>
+          <t>197278</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>254477</t>
+          <t>256535</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>275960</t>
+          <t>276447</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>339104</t>
+          <t>340106</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>203733</t>
+          <t>206269</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>257378</t>
+          <t>257900</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>494798</t>
+          <t>491832</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>578264</t>
+          <t>577683</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>360637</t>
+          <t>355716</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>429458</t>
+          <t>422757</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>250040</t>
+          <t>250155</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>307317</t>
+          <t>307081</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>623899</t>
+          <t>623172</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>709513</t>
+          <t>714352</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>491571</t>
+          <t>488289</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>565359</t>
+          <t>564380</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>338361</t>
+          <t>338839</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>400296</t>
+          <t>399377</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>846061</t>
+          <t>848411</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>943106</t>
+          <t>948392</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6712-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6712-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15439</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18780</t>
+          <t>19725</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11032</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28379</t>
+          <t>28483</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21646</t>
+          <t>21387</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13009</t>
+          <t>13533</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29668</t>
+          <t>29150</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18974</t>
+          <t>18769</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38953</t>
+          <t>39558</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30261</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37115</t>
+          <t>36990</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64197</t>
+          <t>65682</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29779</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52462</t>
+          <t>51906</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14375</t>
+          <t>13959</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32469</t>
+          <t>31869</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48191</t>
+          <t>48600</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76795</t>
+          <t>78097</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80903</t>
+          <t>81597</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107180</t>
+          <t>107015</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65508</t>
+          <t>65860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89614</t>
+          <t>89408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>153881</t>
+          <t>154176</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188704</t>
+          <t>190475</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,34%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32897</t>
+          <t>33012</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58529</t>
+          <t>60507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17567</t>
+          <t>16085</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36882</t>
+          <t>37650</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55366</t>
+          <t>54439</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89698</t>
+          <t>89646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29580</t>
+          <t>30314</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56930</t>
+          <t>56357</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40593</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54772</t>
+          <t>55674</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87860</t>
+          <t>90230</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>143074</t>
+          <t>141071</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>192432</t>
+          <t>192036</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94301</t>
+          <t>94003</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133545</t>
+          <t>133939</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>252203</t>
+          <t>246615</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>310795</t>
+          <t>308392</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>200819</t>
+          <t>197624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>253029</t>
+          <t>250549</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>148900</t>
+          <t>148526</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>194451</t>
+          <t>194037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>363115</t>
+          <t>362853</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>429752</t>
+          <t>434015</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>404304</t>
+          <t>403043</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>466069</t>
+          <t>467914</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207146</t>
+          <t>207353</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>255636</t>
+          <t>255886</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>627682</t>
+          <t>628794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>706862</t>
+          <t>706973</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>14363</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>11812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22155</t>
+          <t>22914</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23573</t>
+          <t>21964</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27993</t>
+          <t>29374</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17148</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40480</t>
+          <t>42199</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19353</t>
+          <t>19429</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41645</t>
+          <t>39972</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>42396</t>
+          <t>43901</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74171</t>
+          <t>74464</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53609</t>
+          <t>54603</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82879</t>
+          <t>82947</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36316</t>
+          <t>37452</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64517</t>
+          <t>67199</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98809</t>
+          <t>99779</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>139278</t>
+          <t>137826</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182348</t>
+          <t>182334</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>220513</t>
+          <t>219507</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>126880</t>
+          <t>124596</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158471</t>
+          <t>158732</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>319994</t>
+          <t>317750</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>369507</t>
+          <t>368892</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,17%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44708</t>
+          <t>45200</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75999</t>
+          <t>75409</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31491</t>
+          <t>30890</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57776</t>
+          <t>58259</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84730</t>
+          <t>84159</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>125325</t>
+          <t>123677</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50771</t>
+          <t>50590</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>83832</t>
+          <t>83989</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28084</t>
+          <t>28283</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53865</t>
+          <t>53893</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>86802</t>
+          <t>83410</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>129959</t>
+          <t>127183</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>193698</t>
+          <t>194428</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>251471</t>
+          <t>250277</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>142484</t>
+          <t>139821</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>190951</t>
+          <t>186881</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>349554</t>
+          <t>344458</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>421567</t>
+          <t>421036</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>303778</t>
+          <t>303390</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>367283</t>
+          <t>366531</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>214748</t>
+          <t>216338</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>272250</t>
+          <t>273865</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>534499</t>
+          <t>533186</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>621035</t>
+          <t>616108</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>692292</t>
+          <t>696094</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>772057</t>
+          <t>768700</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>418672</t>
+          <t>418870</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>483613</t>
+          <t>481577</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1130142</t>
+          <t>1133239</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1235238</t>
+          <t>1235497</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,52%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25777</t>
+          <t>25947</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35943</t>
+          <t>35414</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25747</t>
+          <t>27847</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13959</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35625</t>
+          <t>35072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22599</t>
+          <t>23032</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43555</t>
+          <t>43506</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>16577</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32061</t>
+          <t>32267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43112</t>
+          <t>43129</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69767</t>
+          <t>69363</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21936</t>
+          <t>21558</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41249</t>
+          <t>41793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7737</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>20338</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32958</t>
+          <t>34376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57197</t>
+          <t>58206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36059</t>
+          <t>35938</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59142</t>
+          <t>59445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27896</t>
+          <t>26147</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52120</t>
+          <t>51585</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80011</t>
+          <t>77667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,09%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32307</t>
+          <t>32273</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60526</t>
+          <t>59105</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28016</t>
+          <t>27008</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53124</t>
+          <t>52280</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65166</t>
+          <t>64994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100562</t>
+          <t>103798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66849</t>
+          <t>67500</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101691</t>
+          <t>102977</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56537</t>
+          <t>57655</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86783</t>
+          <t>87146</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131796</t>
+          <t>129690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>177707</t>
+          <t>176495</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>186119</t>
+          <t>188877</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>239597</t>
+          <t>240939</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>132761</t>
+          <t>132067</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>175122</t>
+          <t>176448</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332418</t>
+          <t>334032</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>401830</t>
+          <t>398817</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>250360</t>
+          <t>251098</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>307835</t>
+          <t>306347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>176843</t>
+          <t>176943</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>224415</t>
+          <t>225456</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>444290</t>
+          <t>439722</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>515806</t>
+          <t>511332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>278688</t>
+          <t>280135</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>337281</t>
+          <t>338145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>167223</t>
+          <t>163833</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>212615</t>
+          <t>212821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>460440</t>
+          <t>461615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>537041</t>
+          <t>536467</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,0%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>16001</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19719</t>
+          <t>19131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11749</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28956</t>
+          <t>29034</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34860</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15218</t>
+          <t>15191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32914</t>
+          <t>32578</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34883</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62452</t>
+          <t>60232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46366</t>
+          <t>47590</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>77290</t>
+          <t>76833</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38865</t>
+          <t>39597</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66345</t>
+          <t>65195</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>92772</t>
+          <t>93551</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>131818</t>
+          <t>135329</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68579</t>
+          <t>68471</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>102119</t>
+          <t>100580</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49874</t>
+          <t>51068</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79766</t>
+          <t>78689</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127416</t>
+          <t>126232</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>170745</t>
+          <t>169972</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154482</t>
+          <t>155484</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193238</t>
+          <t>193174</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>142031</t>
+          <t>143264</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>176765</t>
+          <t>176946</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>307179</t>
+          <t>308311</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>360032</t>
+          <t>359616</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52589</t>
+          <t>53945</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85275</t>
+          <t>87299</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44878</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75302</t>
+          <t>73806</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>106272</t>
+          <t>103382</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150786</t>
+          <t>147098</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>104960</t>
+          <t>103743</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>149957</t>
+          <t>149645</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>85276</t>
+          <t>84415</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>121771</t>
+          <t>120732</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>197278</t>
+          <t>198661</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>256535</t>
+          <t>255555</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>276447</t>
+          <t>273657</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>340106</t>
+          <t>339435</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>206269</t>
+          <t>202400</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>257900</t>
+          <t>255662</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>491832</t>
+          <t>494004</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>577683</t>
+          <t>578098</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>355716</t>
+          <t>358976</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>422757</t>
+          <t>428390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>250155</t>
+          <t>249097</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>307081</t>
+          <t>305316</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>623172</t>
+          <t>628513</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>714352</t>
+          <t>715703</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>488289</t>
+          <t>495482</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>564380</t>
+          <t>566357</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>338839</t>
+          <t>337375</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>399377</t>
+          <t>398356</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>848411</t>
+          <t>851234</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>948392</t>
+          <t>945833</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
